--- a/automation/reports/Excel/Summary_Report.xlsx
+++ b/automation/reports/Excel/Summary_Report.xlsx
@@ -499,11 +499,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1500</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>1456</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -566,7 +566,7 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -577,7 +577,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>97.07%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>210.00 seconds</t>
+          <t>0.37 seconds</t>
         </is>
       </c>
     </row>
@@ -633,609 +633,357 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Accessibility</t>
+          <t>Authentication Security</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>95.00%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Authentication</t>
+          <t>Authorization Validation</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>79</v>
+        <v>1</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>98.75%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Authentication Security</t>
+          <t>CSRF Verification</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>96.67%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Authorization</t>
+          <t>Concurrent User Simulation</t>
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>96.67%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Authorization Validation</t>
+          <t>Cookie Validation</t>
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>96.67%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>CRUD Operations</t>
+          <t>Endurance Testing</t>
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>96.25%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>CSRF Verification</t>
+          <t>Input Validation</t>
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>96.67%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Concurrent User Simulation</t>
+          <t>Load Testing</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>97.62%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Cookie Validation</t>
+          <t>OWASP Top 10</t>
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>96.67%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Endurance Testing</t>
+          <t>Response Time Analysis</t>
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>95.35%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Error Handling</t>
+          <t>SQL Injection</t>
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>98.33%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>File Upload</t>
+          <t>Security Headers</t>
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="C26" s="9" t="n">
-        <v>59</v>
+        <v>1</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>98.33%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Forms</t>
+          <t>Sensitive Exposure</t>
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C27" s="9" t="n">
-        <v>77</v>
+        <v>1</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>96.25%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Input Validation</t>
+          <t>Spike Testing</t>
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="C28" s="9" t="n">
-        <v>108</v>
+        <v>2</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>98.18%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Load Testing</t>
+          <t>Stress Testing</t>
         </is>
       </c>
       <c r="B29" s="9" t="n">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="C29" s="9" t="n">
-        <v>41</v>
+        <v>1</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>95.35%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Navigation</t>
+          <t>Throughput Analysis</t>
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>80</v>
+        <v>2</v>
       </c>
       <c r="C30" s="9" t="n">
-        <v>77</v>
+        <v>2</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>96.25%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>OWASP Top 10</t>
+          <t>XSS Prevention</t>
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="C31" s="9" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>96.67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>Performance Smoke</t>
-        </is>
-      </c>
-      <c r="B32" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="C32" s="9" t="n">
-        <v>58</v>
-      </c>
-      <c r="D32" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>96.67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>Response Time Analysis</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="C33" s="9" t="n">
-        <v>42</v>
-      </c>
-      <c r="D33" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>97.67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>Responsive Design</t>
-        </is>
-      </c>
-      <c r="B34" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="C34" s="9" t="n">
-        <v>59</v>
-      </c>
-      <c r="D34" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>98.33%</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>SQL Injection</t>
-        </is>
-      </c>
-      <c r="B35" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="C35" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="D35" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>96.67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>Security Headers</t>
-        </is>
-      </c>
-      <c r="B36" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="C36" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="D36" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>100.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>Sensitive Exposure</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="C37" s="9" t="n">
-        <v>29</v>
-      </c>
-      <c r="D37" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>96.67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>Session Management</t>
-        </is>
-      </c>
-      <c r="B38" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="C38" s="9" t="n">
-        <v>58</v>
-      </c>
-      <c r="D38" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>96.67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Spike Testing</t>
-        </is>
-      </c>
-      <c r="B39" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="C39" s="9" t="n">
-        <v>42</v>
-      </c>
-      <c r="D39" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>97.67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>Stress Testing</t>
-        </is>
-      </c>
-      <c r="B40" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="C40" s="9" t="n">
-        <v>42</v>
-      </c>
-      <c r="D40" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>97.67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Throughput Analysis</t>
-        </is>
-      </c>
-      <c r="B41" s="9" t="n">
-        <v>43</v>
-      </c>
-      <c r="C41" s="9" t="n">
-        <v>42</v>
-      </c>
-      <c r="D41" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>97.67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>UI Validation</t>
-        </is>
-      </c>
-      <c r="B42" s="9" t="n">
-        <v>80</v>
-      </c>
-      <c r="C42" s="9" t="n">
-        <v>78</v>
-      </c>
-      <c r="D42" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>97.50%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>XSS Prevention</t>
-        </is>
-      </c>
-      <c r="B43" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="C43" s="9" t="n">
-        <v>28</v>
-      </c>
-      <c r="D43" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>93.33%</t>
+          <t>100.00%</t>
         </is>
       </c>
     </row>

--- a/automation/reports/Excel/Summary_Report.xlsx
+++ b/automation/reports/Excel/Summary_Report.xlsx
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>20</v>
+        <v>600</v>
       </c>
     </row>
     <row r="5">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>20</v>
+        <v>600</v>
       </c>
     </row>
     <row r="6">
@@ -589,7 +589,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>0.37 seconds</t>
+          <t>0.34 seconds</t>
         </is>
       </c>
     </row>
@@ -637,10 +637,10 @@
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>0</v>
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C16" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D16" s="9" t="n">
         <v>0</v>
@@ -679,10 +679,10 @@
         </is>
       </c>
       <c r="B17" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C17" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D17" s="9" t="n">
         <v>0</v>
@@ -700,10 +700,10 @@
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="D18" s="9" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="B19" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C19" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D19" s="9" t="n">
         <v>0</v>
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="D20" s="9" t="n">
         <v>0</v>
@@ -763,10 +763,10 @@
         </is>
       </c>
       <c r="B21" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C21" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D21" s="9" t="n">
         <v>0</v>
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>0</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C23" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D23" s="9" t="n">
         <v>0</v>
@@ -826,10 +826,10 @@
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>0</v>
@@ -847,10 +847,10 @@
         </is>
       </c>
       <c r="B25" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C25" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D25" s="9" t="n">
         <v>0</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B26" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C26" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D26" s="9" t="n">
         <v>0</v>
@@ -889,10 +889,10 @@
         </is>
       </c>
       <c r="B27" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C27" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D27" s="9" t="n">
         <v>0</v>
@@ -910,10 +910,10 @@
         </is>
       </c>
       <c r="B28" s="9" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="C28" s="9" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="D28" s="9" t="n">
         <v>0</v>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="B29" s="9" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="C29" s="9" t="n">
-        <v>1</v>
+        <v>43</v>
       </c>
       <c r="D29" s="9" t="n">
         <v>0</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="C30" s="9" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="D30" s="9" t="n">
         <v>0</v>
@@ -973,10 +973,10 @@
         </is>
       </c>
       <c r="B31" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="C31" s="9" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D31" s="9" t="n">
         <v>0</v>

--- a/automation/reports/Excel/Summary_Report.xlsx
+++ b/automation/reports/Excel/Summary_Report.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>600</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>600</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="6">
@@ -589,7 +589,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>0.34 seconds</t>
+          <t>4.11 seconds</t>
         </is>
       </c>
     </row>
@@ -633,14 +633,14 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Authentication Security</t>
+          <t>Authentication</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="C15" s="9" t="n">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="D15" s="9" t="n">
         <v>0</v>
@@ -654,7 +654,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Authorization Validation</t>
+          <t>Authentication Security</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
@@ -675,7 +675,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>CSRF Verification</t>
+          <t>Authorization Validation</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
@@ -696,14 +696,14 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Concurrent User Simulation</t>
+          <t>Background Sync</t>
         </is>
       </c>
       <c r="B18" s="9" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C18" s="9" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="D18" s="9" t="n">
         <v>0</v>
@@ -717,7 +717,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Cookie Validation</t>
+          <t>Biometrics</t>
         </is>
       </c>
       <c r="B19" s="9" t="n">
@@ -738,14 +738,14 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Endurance Testing</t>
+          <t>CSRF Verification</t>
         </is>
       </c>
       <c r="B20" s="9" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C20" s="9" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D20" s="9" t="n">
         <v>0</v>
@@ -759,7 +759,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Input Validation</t>
+          <t>Camera Integration</t>
         </is>
       </c>
       <c r="B21" s="9" t="n">
@@ -780,14 +780,14 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Load Testing</t>
+          <t>Concurrent User Simulation</t>
         </is>
       </c>
       <c r="B22" s="9" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D22" s="9" t="n">
         <v>0</v>
@@ -801,7 +801,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>OWASP Top 10</t>
+          <t>Cookie Validation</t>
         </is>
       </c>
       <c r="B23" s="9" t="n">
@@ -822,14 +822,14 @@
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Response Time Analysis</t>
+          <t>Data Models Validation</t>
         </is>
       </c>
       <c r="B24" s="9" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C24" s="9" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D24" s="9" t="n">
         <v>0</v>
@@ -843,7 +843,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>SQL Injection</t>
+          <t>Date Formatting</t>
         </is>
       </c>
       <c r="B25" s="9" t="n">
@@ -864,7 +864,7 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Security Headers</t>
+          <t>Deep Linking</t>
         </is>
       </c>
       <c r="B26" s="9" t="n">
@@ -885,7 +885,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Sensitive Exposure</t>
+          <t>Device Permissions</t>
         </is>
       </c>
       <c r="B27" s="9" t="n">
@@ -906,7 +906,7 @@
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Spike Testing</t>
+          <t>Endurance Testing</t>
         </is>
       </c>
       <c r="B28" s="9" t="n">
@@ -927,14 +927,14 @@
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Stress Testing</t>
+          <t>Helper Utils</t>
         </is>
       </c>
       <c r="B29" s="9" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C29" s="9" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D29" s="9" t="n">
         <v>0</v>
@@ -948,14 +948,14 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Throughput Analysis</t>
+          <t>Input Sanitizers</t>
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C30" s="9" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="D30" s="9" t="n">
         <v>0</v>
@@ -969,19 +969,502 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
+          <t>Input Validation</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C31" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Load Testing</t>
+        </is>
+      </c>
+      <c r="B32" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="C32" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>Local Database</t>
+        </is>
+      </c>
+      <c r="B33" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C33" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>Local Storage</t>
+        </is>
+      </c>
+      <c r="B34" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C34" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>Native App Launch</t>
+        </is>
+      </c>
+      <c r="B35" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C35" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Navigation</t>
+        </is>
+      </c>
+      <c r="B36" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="C36" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>Network Clients</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C37" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>OCR Processing Logic</t>
+        </is>
+      </c>
+      <c r="B38" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C38" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>OWASP Top 10</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C39" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Offline Mode</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C40" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Patient</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="n">
+        <v>140</v>
+      </c>
+      <c r="C41" s="9" t="n">
+        <v>140</v>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Push Notifications</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C42" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>Repository Implementation</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C43" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>Response Time Analysis</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="C44" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>Riverpod Providers</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>SQL Injection</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C46" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Screen Navigation</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C47" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Security Headers</t>
+        </is>
+      </c>
+      <c r="B48" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C48" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Sensitive Exposure</t>
+        </is>
+      </c>
+      <c r="B49" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C49" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>Spike Testing</t>
+        </is>
+      </c>
+      <c r="B50" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="C50" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>State Management</t>
+        </is>
+      </c>
+      <c r="B51" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C51" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>Stress Testing</t>
+        </is>
+      </c>
+      <c r="B52" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="C52" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Throughput Analysis</t>
+        </is>
+      </c>
+      <c r="B53" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="C53" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>100.00%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
           <t>XSS Prevention</t>
         </is>
       </c>
-      <c r="B31" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="C31" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="D31" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
+      <c r="B54" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C54" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>100.00%</t>
         </is>
